--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110577834</v>
+        <v>110866072</v>
       </c>
       <c r="B8" t="n">
-        <v>56404</v>
+        <v>101703</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1447,23 +1447,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Bergalund (Bergalund), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583650.0028709093</v>
+        <v>583510.2994166655</v>
       </c>
       <c r="R8" t="n">
-        <v>6528484.04706091</v>
+        <v>6528549.26438573</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1493,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,22 +1523,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110866072</v>
+        <v>110886288</v>
       </c>
       <c r="B9" t="n">
-        <v>101703</v>
+        <v>56404</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,25 +1547,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1567,29 +1573,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergalund (Bergalund), Srm</t>
+          <t>Kullen ö om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583510.2994166655</v>
+        <v>583639.3377232057</v>
       </c>
       <c r="R9" t="n">
-        <v>6528549.26438573</v>
+        <v>6528402.64362955</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1618,7 +1630,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1640,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,26 +1651,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110886288</v>
+        <v>110885947</v>
       </c>
       <c r="B10" t="n">
-        <v>56404</v>
+        <v>5107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,20 +1689,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>102185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1688,20 +1710,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1763,12 +1778,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>i gammal sälg</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1797,10 +1818,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110885947</v>
+        <v>110886277</v>
       </c>
       <c r="B11" t="n">
-        <v>5107</v>
+        <v>56414</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,20 +1830,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102185</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1830,13 +1851,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1898,18 +1926,12 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110886277</v>
+        <v>110886322</v>
       </c>
       <c r="B12" t="n">
-        <v>56414</v>
+        <v>101703</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1950,25 +1972,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1976,17 +1998,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2046,12 +2064,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>avröjd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2080,10 +2104,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110886322</v>
+        <v>110885428</v>
       </c>
       <c r="B13" t="n">
-        <v>101703</v>
+        <v>106989</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,20 +2116,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2115,15 +2139,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -2136,13 +2164,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583639.3377232057</v>
+        <v>583670.5052294435</v>
       </c>
       <c r="R13" t="n">
-        <v>6528402.64362955</v>
+        <v>6528446.232591932</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2182,11 +2210,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>avröjd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2224,10 +2247,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110885428</v>
+        <v>111215677</v>
       </c>
       <c r="B14" t="n">
-        <v>106989</v>
+        <v>96382</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2236,61 +2259,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>223619</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583670.5052294435</v>
+        <v>583650.0028709093</v>
       </c>
       <c r="R14" t="n">
-        <v>6528446.232591932</v>
+        <v>6528484.04706091</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2314,22 +2325,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,35 +2353,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111215677</v>
+        <v>111215642</v>
       </c>
       <c r="B15" t="n">
-        <v>96382</v>
+        <v>98446</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2383,22 +2384,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223619</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2450,7 +2455,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2460,7 +2465,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2485,131 +2490,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>111215642</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98446</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>583650.0028709093</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6528484.04706091</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110886288</v>
+        <v>110885428</v>
       </c>
       <c r="B9" t="n">
-        <v>56404</v>
+        <v>106989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,39 +1551,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583639.3377232057</v>
+        <v>583670.5052294435</v>
       </c>
       <c r="R9" t="n">
-        <v>6528402.64362955</v>
+        <v>6528446.232591932</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1649,6 +1649,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1677,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110885947</v>
+        <v>111215677</v>
       </c>
       <c r="B10" t="n">
-        <v>5107</v>
+        <v>96382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,50 +1694,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102185</v>
+        <v>223619</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583639.3377232057</v>
+        <v>583650.0028709093</v>
       </c>
       <c r="R10" t="n">
-        <v>6528402.64362955</v>
+        <v>6528484.04706091</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1760,27 +1756,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>i gammal sälg</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,35 +1784,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110886277</v>
+        <v>111215642</v>
       </c>
       <c r="B11" t="n">
-        <v>56414</v>
+        <v>98446</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1830,25 +1811,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1856,35 +1837,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583639.3377232057</v>
+        <v>583650.0028709093</v>
       </c>
       <c r="R11" t="n">
-        <v>6528402.64362955</v>
+        <v>6528484.04706091</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1908,22 +1881,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1932,564 +1905,22 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>110886322</v>
-      </c>
-      <c r="B12" t="n">
-        <v>101703</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Kullen ö om, Srm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>583639.3377232057</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6528402.64362955</v>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>avröjd</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>110885428</v>
-      </c>
-      <c r="B13" t="n">
-        <v>106989</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220299</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Kullen ö om, Srm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>583670.5052294435</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6528446.232591932</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>111215677</v>
-      </c>
-      <c r="B14" t="n">
-        <v>96382</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>223619</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ängsnattviol</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>583650.0028709093</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6528484.04706091</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>111215642</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98446</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>583650.0028709093</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6528484.04706091</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110221107</v>
+        <v>110234754</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R2" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +780,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,16 +801,11 @@
         <v>110221078</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -844,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R3" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +874,9 @@
           <t>2023-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,47 +903,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110234773</v>
+        <v>110234764</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100890</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mulmknäppare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Elater ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R4" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1040,12 +1023,7 @@
         <v>110234790</v>
       </c>
       <c r="B5" t="n">
-        <v>9310</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R5" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1159,48 +1137,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110234764</v>
+        <v>110221107</v>
       </c>
       <c r="B6" t="n">
-        <v>8778</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100890</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mulmknäppare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Elater ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R6" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,22 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,15 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110234754</v>
+        <v>110885428</v>
       </c>
       <c r="B7" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,53 +1254,57 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen ö om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583651</v>
+        <v>583671</v>
       </c>
       <c r="R7" t="n">
-        <v>6528484</v>
+        <v>6528446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,22 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,33 +1342,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110866072</v>
+        <v>110234773</v>
       </c>
       <c r="B8" t="n">
-        <v>101703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,32 +1401,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergalund (Bergalund), Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583510.2994166655</v>
+        <v>583651</v>
       </c>
       <c r="R8" t="n">
-        <v>6528549.26438573</v>
+        <v>6528484</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,22 +1444,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,50 +1468,46 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110885428</v>
+        <v>110866072</v>
       </c>
       <c r="B9" t="n">
-        <v>106989</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1570,38 +1517,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Bergalund, Bergalund, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583670.5052294435</v>
+        <v>583510</v>
       </c>
       <c r="R9" t="n">
-        <v>6528446.232591932</v>
+        <v>6528549</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,44 +1590,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111215677</v>
+        <v>111215642</v>
       </c>
       <c r="B10" t="n">
-        <v>96382</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,22 +1619,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223619</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1726,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R10" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1761,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1771,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,15 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111215642</v>
+        <v>111215677</v>
       </c>
       <c r="B11" t="n">
-        <v>98446</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,26 +1739,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>223619</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1851,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583650.0028709093</v>
+        <v>583651</v>
       </c>
       <c r="R11" t="n">
-        <v>6528484.04706091</v>
+        <v>6528484</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1886,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1896,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110234754</v>
+        <v>110851340</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R2" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110221078</v>
+        <v>109849917</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,25 +814,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R3" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,12 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,54 +901,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110234764</v>
+        <v>110851317</v>
       </c>
       <c r="B4" t="n">
-        <v>8882</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100890</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mulmknäppare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Elater ferrugineus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R4" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,22 +970,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +994,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110234790</v>
+        <v>109849948</v>
       </c>
       <c r="B5" t="n">
-        <v>9414</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1023,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105076</v>
+        <v>100082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,21 +1045,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R5" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,53 +1127,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110221107</v>
+        <v>110392950</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R6" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,12 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1243,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110885428</v>
+        <v>110851372</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,57 +1249,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583671</v>
+        <v>583497</v>
       </c>
       <c r="R7" t="n">
-        <v>6528446</v>
+        <v>6528368</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,12 +1307,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,82 +1331,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110234773</v>
+        <v>107325305</v>
       </c>
       <c r="B8" t="n">
-        <v>104628</v>
+        <v>57794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R8" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,22 +1426,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1450,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1484,363 +1465,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>110866072</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104628</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bergalund, Bergalund, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>583510</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6528549</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>111215642</v>
-      </c>
-      <c r="B10" t="n">
-        <v>101228</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>111215677</v>
-      </c>
-      <c r="B11" t="n">
-        <v>99154</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>223619</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ängsnattviol</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110851340</v>
+        <v>110234754</v>
       </c>
       <c r="B2" t="n">
-        <v>57879</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100034</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R2" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +798,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109849917</v>
+        <v>110221078</v>
       </c>
       <c r="B3" t="n">
-        <v>57966</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,25 +826,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R3" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,49 +903,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110851317</v>
+        <v>110234764</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>8882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100890</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Mulmknäppare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Elater ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R4" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,6 +1001,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109849948</v>
+        <v>110234790</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>9414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100082</v>
+        <v>105076</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,20 +1053,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R5" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,22 +1094,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1118,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,49 +1137,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110392950</v>
+        <v>110221107</v>
       </c>
       <c r="B6" t="n">
-        <v>57825</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R6" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,22 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110851372</v>
+        <v>110885428</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,41 +1254,57 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100100</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Kullen ö om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583497</v>
+        <v>583671</v>
       </c>
       <c r="R7" t="n">
-        <v>6528368</v>
+        <v>6528446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,22 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,75 +1342,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107325305</v>
+        <v>110234773</v>
       </c>
       <c r="B8" t="n">
-        <v>57794</v>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R8" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,22 +1444,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,6 +1468,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,6 +1484,363 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110866072</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergalund, Bergalund, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583510</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6528549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111215642</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111215677</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,64 +672,57 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110234754</v>
+        <v>110851340</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R2" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,30 +788,35 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110851340</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110221078</v>
+        <v>109849917</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,25 +824,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R3" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,57 +908,57 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109849917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110234764</v>
+        <v>110851317</v>
       </c>
       <c r="B4" t="n">
-        <v>8882</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100890</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mulmknäppare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Elater ferrugineus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R4" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,22 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1009,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,13 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110851317</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110234790</v>
+        <v>109849948</v>
       </c>
       <c r="B5" t="n">
-        <v>9414</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1043,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105076</v>
+        <v>100082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,21 +1065,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R5" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,22 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1129,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,56 +1144,57 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109849948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110221107</v>
+        <v>110392950</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R6" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,12 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,13 +1260,18 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392950</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110885428</v>
+        <v>110851372</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,57 +1279,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583671</v>
+        <v>583497</v>
       </c>
       <c r="R7" t="n">
-        <v>6528446</v>
+        <v>6528368</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,12 +1337,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,82 +1361,80 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110851372</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110234773</v>
+        <v>107325305</v>
       </c>
       <c r="B8" t="n">
-        <v>104628</v>
+        <v>57794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R8" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,22 +1461,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1485,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1484,365 +1500,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>110866072</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104628</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bergalund, Bergalund, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>583510</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6528549</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>111215642</v>
-      </c>
-      <c r="B10" t="n">
-        <v>101228</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>111215677</v>
-      </c>
-      <c r="B11" t="n">
-        <v>99154</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>223619</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ängsnattviol</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107325305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110851340</v>
+        <v>110234754</v>
       </c>
       <c r="B2" t="n">
-        <v>57879</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100034</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R2" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,33 +802,33 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110851340</t>
+          <t>https://artportalen.se/Sighting/110234754</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109849917</v>
+        <v>110221078</v>
       </c>
       <c r="B3" t="n">
-        <v>57966</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,25 +836,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R3" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,22 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,55 +912,60 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109849917</t>
+          <t>https://artportalen.se/Sighting/110221078</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110851317</v>
+        <v>110234764</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>8882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100890</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Mulmknäppare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Elater ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R4" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,22 +992,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,6 +1016,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,16 +1034,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110851317</t>
+          <t>https://artportalen.se/Sighting/110234764</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109849948</v>
+        <v>110234790</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>9414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100082</v>
+        <v>105076</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,20 +1073,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R5" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,6 +1138,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,55 +1156,59 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109849948</t>
+          <t>https://artportalen.se/Sighting/110234790</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110392950</v>
+        <v>110221107</v>
       </c>
       <c r="B6" t="n">
-        <v>57825</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R6" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,22 +1235,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,6 +1249,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,16 +1267,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110392950</t>
+          <t>https://artportalen.se/Sighting/110221107</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110851372</v>
+        <v>110885428</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,41 +1284,57 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100100</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Kullen ö om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583497</v>
+        <v>583671</v>
       </c>
       <c r="R7" t="n">
-        <v>6528368</v>
+        <v>6528446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,22 +1358,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,80 +1372,87 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110851372</t>
+          <t>https://artportalen.se/Sighting/110885428</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107325305</v>
+        <v>110234773</v>
       </c>
       <c r="B8" t="n">
-        <v>57794</v>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullen Tegnebol, Srm</t>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583497</v>
+        <v>583651</v>
       </c>
       <c r="R8" t="n">
-        <v>6528368</v>
+        <v>6528484</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,22 +1479,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,6 +1503,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,7 +1521,379 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107325305</t>
+          <t>https://artportalen.se/Sighting/110234773</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110866072</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergalund, Bergalund, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583510</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6528549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110866072</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111215642</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215642</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111215677</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215677</t>
         </is>
       </c>
     </row>
@@ -1515,6 +1906,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,61 +680,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110234754</v>
+        <v>110851340</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R2" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,33 +790,33 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234754</t>
+          <t>https://artportalen.se/Sighting/110851340</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110221078</v>
+        <v>109849917</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,25 +824,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R3" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,60 +910,55 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110221078</t>
+          <t>https://artportalen.se/Sighting/109849917</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110234764</v>
+        <v>110851317</v>
       </c>
       <c r="B4" t="n">
-        <v>8882</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100890</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mulmknäppare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Elater ferrugineus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R4" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,22 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1009,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,16 +1026,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234764</t>
+          <t>https://artportalen.se/Sighting/110851317</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110234790</v>
+        <v>109849948</v>
       </c>
       <c r="B5" t="n">
-        <v>9414</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1043,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105076</v>
+        <v>100082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,21 +1065,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R5" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,22 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1129,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,59 +1146,55 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234790</t>
+          <t>https://artportalen.se/Sighting/109849948</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110221107</v>
+        <v>110392950</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R6" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,12 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,16 +1262,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110221107</t>
+          <t>https://artportalen.se/Sighting/110392950</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110885428</v>
+        <v>110851372</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,57 +1279,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583671</v>
+        <v>583497</v>
       </c>
       <c r="R7" t="n">
-        <v>6528446</v>
+        <v>6528368</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,12 +1337,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,87 +1361,80 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110885428</t>
+          <t>https://artportalen.se/Sighting/110851372</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110234773</v>
+        <v>107325305</v>
       </c>
       <c r="B8" t="n">
-        <v>104628</v>
+        <v>57794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R8" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,22 +1461,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1485,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1521,379 +1502,7 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234773</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>110866072</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104628</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bergalund, Bergalund, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>583510</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6528549</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anna Sahlberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/110866072</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>111215642</v>
-      </c>
-      <c r="B10" t="n">
-        <v>101228</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/111215642</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>111215677</v>
-      </c>
-      <c r="B11" t="n">
-        <v>99154</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>223619</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ängsnattviol</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>583651</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6528484</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Björkvik</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Daniel Franzén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/111215677</t>
+          <t>https://artportalen.se/Sighting/107325305</t>
         </is>
       </c>
     </row>
@@ -1906,9 +1515,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
